--- a/data/manual/reglas.xlsx
+++ b/data/manual/reglas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e_edobru\Desktop\Bancomext\Aranceles\data\manual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE79E7B0-2B9F-4148-9FF1-D4422063B3A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A5A5815-9928-49C3-B4E9-E490E17FDB59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{9A179E33-413E-4389-9CC5-66FB5ECDE290}"/>
   </bookViews>
